--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GA7thFinal_Orora\2_Documents\데이터 테이블\베타 밸런스\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5AF54-1518-4014-9678-D8065C944B87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5656C72-3B46-44EE-AAF4-6F0AF491AE5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -1658,14 +1658,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2790,23 +2790,23 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A4" s="18" t="s">
@@ -3060,7 +3060,7 @@
       <c r="AG5" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="AH5" s="45" t="s">
+      <c r="AH5" s="43" t="s">
         <v>312</v>
       </c>
       <c r="AI5" s="19" t="s">
@@ -3081,10 +3081,10 @@
       <c r="AN5" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="AP5" s="45" t="s">
+      <c r="AP5" s="43" t="s">
         <v>320</v>
       </c>
       <c r="AQ5" s="18" t="s">
@@ -5807,11 +5807,11 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
@@ -6475,6 +6475,9 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -6493,6 +6496,9 @@
       <c r="Q19" s="5"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A20" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="B20" s="8" t="s">
         <v>156</v>
       </c>
@@ -6543,9 +6549,6 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -6564,9 +6567,6 @@
       <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A22" s="8" t="s">
-        <v>155</v>
-      </c>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5656C72-3B46-44EE-AAF4-6F0AF491AE5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -1786,8 +1780,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -1817,7 +1811,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1875,8 +1869,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -1906,7 +1900,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1964,8 +1958,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -2003,7 +1997,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2061,8 +2055,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -2078,7 +2072,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2136,8 +2130,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -2153,7 +2147,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2211,8 +2205,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -2266,7 +2260,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2324,8 +2318,8 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr anchor="ctr"/>
+      <a:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr">
@@ -2379,7 +2373,7 @@
           </a:r>
           <a:endParaRPr/>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -5780,7 +5774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5798,7 +5792,6 @@
     <col min="14" max="14" width="8.83203125" style="8" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="8" customWidth="1"/>
     <col min="16" max="38" width="15.58203125" style="8" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
@@ -5930,21 +5923,41 @@
         <v>139</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E6" s="17">
         <v>2</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+      <c r="F6" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="I6" s="17">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="K6" s="17">
+        <v>0</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="O6" s="17">
+        <v>0</v>
+      </c>
       <c r="P6" s="17">
         <v>4</v>
       </c>
@@ -5960,7 +5973,7 @@
         <v>140</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
@@ -5990,7 +6003,7 @@
         <v>5</v>
       </c>
       <c r="N7" s="39" t="s">
-        <v>297</v>
+        <v>15</v>
       </c>
       <c r="O7" s="17">
         <v>2</v>
@@ -6010,7 +6023,7 @@
         <v>141</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="E8" s="39">
         <v>2</v>
@@ -6039,8 +6052,12 @@
       <c r="M8" s="17">
         <v>3</v>
       </c>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="O8" s="17">
+        <v>0</v>
+      </c>
       <c r="P8" s="17">
         <v>4</v>
       </c>
@@ -6062,7 +6079,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>298</v>
+        <v>14</v>
       </c>
       <c r="G9" s="17">
         <v>6</v>
@@ -6085,8 +6102,12 @@
       <c r="M9" s="17">
         <v>3</v>
       </c>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="O9" s="17">
+        <v>0</v>
+      </c>
       <c r="P9" s="17">
         <v>4</v>
       </c>
@@ -6102,7 +6123,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>298</v>
+        <v>14</v>
       </c>
       <c r="E10" s="17">
         <v>2</v>
@@ -6155,26 +6176,38 @@
         <v>14</v>
       </c>
       <c r="E11" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I11" s="17">
         <v>6</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
+      <c r="J11" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="O11" s="17">
+        <v>0</v>
+      </c>
       <c r="P11" s="17">
         <v>4</v>
       </c>
@@ -6190,7 +6223,7 @@
         <v>299</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="E12" s="17">
         <v>1</v>
@@ -6213,10 +6246,18 @@
       <c r="K12" s="17">
         <v>5</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="17"/>
+      <c r="L12" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="M12" s="17">
+        <v>0</v>
+      </c>
+      <c r="N12" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="O12" s="17">
+        <v>0</v>
+      </c>
       <c r="P12" s="17">
         <v>4</v>
       </c>
@@ -6255,10 +6296,18 @@
       <c r="K13" s="17">
         <v>6</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="17"/>
+      <c r="L13" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
       <c r="P13" s="17">
         <v>4</v>
       </c>
@@ -6291,12 +6340,24 @@
       <c r="I14" s="17">
         <v>6</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="17"/>
+      <c r="J14" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="K14" s="17">
+        <v>0</v>
+      </c>
+      <c r="L14" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="M14" s="17">
+        <v>0</v>
+      </c>
+      <c r="N14" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="O14" s="17">
+        <v>0</v>
+      </c>
       <c r="P14" s="17">
         <v>5</v>
       </c>
@@ -6330,12 +6391,24 @@
       <c r="I15" s="40">
         <v>5</v>
       </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
+      <c r="J15" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="K15" s="40">
+        <v>0</v>
+      </c>
+      <c r="L15" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="M15" s="40">
+        <v>0</v>
+      </c>
+      <c r="N15" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="O15" s="40">
+        <v>0</v>
+      </c>
       <c r="P15" s="17">
         <v>4</v>
       </c>
@@ -6352,7 +6425,7 @@
         <v>148</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>298</v>
+        <v>14</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
@@ -6369,12 +6442,24 @@
       <c r="I16" s="40">
         <v>3</v>
       </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
+      <c r="J16" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="K16" s="40">
+        <v>0</v>
+      </c>
+      <c r="L16" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="M16" s="40">
+        <v>0</v>
+      </c>
+      <c r="N16" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="O16" s="40">
+        <v>0</v>
+      </c>
       <c r="P16" s="17">
         <v>4</v>
       </c>
@@ -6390,7 +6475,7 @@
         <v>150</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="E17" s="17">
         <v>4</v>
@@ -6419,8 +6504,12 @@
       <c r="M17" s="38">
         <v>3</v>
       </c>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
+      <c r="N17" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="O17" s="38">
+        <v>0</v>
+      </c>
       <c r="P17" s="17">
         <v>4</v>
       </c>
@@ -6436,7 +6525,7 @@
         <v>163</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="E18" s="17">
         <v>1</v>
@@ -6460,13 +6549,17 @@
         <v>4</v>
       </c>
       <c r="L18" s="41" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="M18" s="38">
         <v>2</v>
       </c>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
+      <c r="N18" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="O18" s="38">
+        <v>0</v>
+      </c>
       <c r="P18" s="17">
         <v>4</v>
       </c>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 2구역 이벤트 전투 테이블.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GA7thFinal_Orora\2_Documents\데이터 테이블\베타 밸런스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5656C72-3B46-44EE-AAF4-6F0AF491AE5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D5AF54-1518-4014-9678-D8065C944B87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="324">
   <si>
     <t>2구역 메인/서브 이벤트 전투 테이블</t>
   </si>
@@ -1344,6 +1344,9 @@
   </si>
   <si>
     <t>EnemySkill3SubValue</t>
+  </si>
+  <si>
+    <t>{3,7}</t>
   </si>
 </sst>
 </file>
@@ -1658,14 +1661,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2790,23 +2793,23 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A4" s="18" t="s">
@@ -3060,7 +3063,7 @@
       <c r="AG5" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="AH5" s="43" t="s">
+      <c r="AH5" s="45" t="s">
         <v>312</v>
       </c>
       <c r="AI5" s="19" t="s">
@@ -3081,10 +3084,10 @@
       <c r="AN5" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="AO5" s="43" t="s">
+      <c r="AO5" s="45" t="s">
         <v>319</v>
       </c>
-      <c r="AP5" s="43" t="s">
+      <c r="AP5" s="45" t="s">
         <v>320</v>
       </c>
       <c r="AQ5" s="18" t="s">
@@ -5137,8 +5140,8 @@
       <c r="AB25" s="18">
         <v>1</v>
       </c>
-      <c r="AC25" s="18">
-        <v>2</v>
+      <c r="AC25" s="18" t="s">
+        <v>323</v>
       </c>
       <c r="AD25" s="18">
         <v>0</v>
@@ -5362,8 +5365,8 @@
       <c r="AM27" s="18">
         <v>1</v>
       </c>
-      <c r="AN27" s="18">
-        <v>2</v>
+      <c r="AN27" s="18" t="s">
+        <v>323</v>
       </c>
       <c r="AO27" s="18">
         <v>0</v>
@@ -5518,8 +5521,8 @@
       <c r="Q29" s="32">
         <v>1</v>
       </c>
-      <c r="R29" s="32">
-        <v>2</v>
+      <c r="R29" s="32" t="s">
+        <v>323</v>
       </c>
       <c r="S29" s="32">
         <v>0</v>
@@ -5807,11 +5810,11 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
